--- a/reports/集团总公司_现金流量表_2025-04.xlsx
+++ b/reports/集团总公司_现金流量表_2025-04.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>195000000</v>
+        <v>194644130</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>733200000</v>
+        <v>731429872</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4010179</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>15111220</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2007332</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7520781</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>999468</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3775145</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>805043</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>3011674</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>598526</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2261902</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>402925</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1508179</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>299267</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1129213</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>201256</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>755114</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>499751</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1880064</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>252192</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>949311</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>159386</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>597693</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>530000</v>
+        <v>529011</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1992800</v>
+        <v>1996908</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3600000</v>
+        <v>3611691</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>13536000</v>
+        <v>13515304</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>199130000</v>
+        <v>209020157</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>120000000</v>
+        <v>119565094</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>451200000</v>
+        <v>450298056</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1339521</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>5036669</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1001495</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3759401</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>667655</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2518213</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>502325</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1880726</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>332887</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1257871</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>253003</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>946436</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>24200000</v>
+        <v>24079706</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>90992000</v>
+        <v>90973394</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11200000</v>
+        <v>11254691</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>42112000</v>
+        <v>42153035</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5100000</v>
+        <v>5078147</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>19176000</v>
+        <v>19144505</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>160500000</v>
+        <v>164074524</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>38630000</v>
+        <v>44945633</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>238863</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>960000</v>
+        <v>960535</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2090043</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>8400000</v>
+        <v>8391652</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1285105</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>5120000</v>
+        <v>5128472</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2328906</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>20027026</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>80000000</v>
+        <v>80192416</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2900741</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>11600000</v>
+        <v>11571960</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14173936</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>56800000</v>
+        <v>56923629</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>517414</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2080000</v>
+        <v>2078989</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20544440</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18215534</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4696083</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>18800000</v>
+        <v>18754178</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7517385</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>30000000</v>
+        <v>29938602</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7472920</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>30000000</v>
+        <v>30045404</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>241087</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>960000</v>
+        <v>959211</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12454555</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6129827</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>24400000</v>
+        <v>24417987</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6073765</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>24400000</v>
+        <v>24364815</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>1003262</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>4000000</v>
+        <v>4007985</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>870266</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3480000</v>
+        <v>3488499</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>125163</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>500000</v>
+        <v>498857</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7258252</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5196303</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>25665000</v>
+        <v>31926402</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>25665000</v>
+        <v>31926402</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
